--- a/data.mn/public/datasets/mongolbank-money-supply-m2.xlsx
+++ b/data.mn/public/datasets/mongolbank-money-supply-m2.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="English" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Монгол" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3965,4 +3966,3564 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B354"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>огноо</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>м2_тэрбум_төгрөг</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1997-03-01</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>114.508</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1997-04-01</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>123.396</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1997-05-01</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>133.094</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1997-06-01</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>137.858</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1997-07-01</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>152.846</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1997-08-01</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>150.59</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1997-09-01</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>151.569</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1997-10-01</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>155.751</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1997-11-01</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>156.346</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1997-12-01</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>170.065</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1998-01-01</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>157.332</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1998-02-01</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>161.957</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1998-03-01</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>153.628</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1998-04-01</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>156.14</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1998-05-01</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>166.498</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1998-06-01</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>160.226</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1998-07-01</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>168.529</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1998-08-01</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>165.219</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1998-09-01</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>165.993</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1998-10-01</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>162.604</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1998-11-01</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>160.563</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1998-12-01</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>167.25</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1999-01-01</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>155.207</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>1999-02-01</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>161.917</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>1999-03-01</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>153.683</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>1999-04-01</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>165.555</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>1999-05-01</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>175.581</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>1999-06-01</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>184.635</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>1999-07-01</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>196.173</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>1999-08-01</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>196.858</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>1999-09-01</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>198.94</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>1999-10-01</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>203.016</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>1999-11-01</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>207.047</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>1999-12-01</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>220.167</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2000-01-01</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>211.33</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2000-02-01</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>207.542</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2000-03-01</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>222.434</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2000-04-01</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>234.587</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2000-05-01</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>242.989</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2000-06-01</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>255.258</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2000-07-01</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>251.841</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2000-08-01</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>256.864</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2000-09-01</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>264.49</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2000-10-01</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>257.529</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2000-11-01</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>245.548</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2000-12-01</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>258.843</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2001-01-01</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>250.001</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2001-02-01</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>258.148</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2001-03-01</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>270.541</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2001-04-01</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>282.745</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2001-05-01</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>299.892</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2001-06-01</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>313.946</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2001-07-01</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>310.976</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2001-08-01</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>321.088</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2001-09-01</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>317.428</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2001-10-01</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>316.102</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2001-11-01</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>315.864</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2001-12-01</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>331.064</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2002-01-01</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>324.736</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2002-02-01</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>375.321</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2002-03-01</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>345.872</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2002-04-01</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>369.435</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2002-05-01</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>388.396</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2002-06-01</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>401.164</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2002-07-01</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>421.873</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2002-08-01</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>431.021</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2002-09-01</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>437.671</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2002-10-01</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>439.856</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2002-11-01</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>447.784</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2002-12-01</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>470.299</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2003-01-01</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>487.742</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2003-02-01</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>490.489</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2003-03-01</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>504.293</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2003-04-01</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>530.569</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2003-05-01</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>542.45</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2003-06-01</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>557.744</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2003-07-01</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>582.405</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2003-08-01</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>588.513</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2003-09-01</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>609.367</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2003-10-01</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>623.413</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2003-11-01</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>627.501</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2003-12-01</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>703.332</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>694.2430000000001</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2004-02-01</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>721.312</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2004-03-01</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>740.191</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2004-04-01</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>774.876</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2004-05-01</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>789.378</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2004-06-01</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>812.171</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2004-07-01</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>813.572</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2004-08-01</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>842.465</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2004-09-01</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>827.25</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2004-10-01</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>831.122</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2004-11-01</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>839.548</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2004-12-01</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>847.032</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2005-01-01</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>858.735</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2005-02-01</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>860.115</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2005-03-01</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>892.974</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2005-04-01</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>932.476</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2005-05-01</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>972.133</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2005-06-01</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>1009.588</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2005-07-01</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>1040.144</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2005-08-01</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>1081.203</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2005-09-01</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>1112.375</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2005-10-01</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>1112.799</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2005-11-01</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>1110.62</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2005-12-01</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>1140.139</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2006-01-01</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>1146.571</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2006-02-01</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>1145.588</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2006-03-01</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>1191.245</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2006-04-01</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>1251.241</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2006-05-01</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>1403.989</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2006-06-01</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>1454.188</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2006-07-01</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>1478.259</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2006-08-01</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>1495.323</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2006-09-01</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>1542.757</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2006-10-01</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>1548.79</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2006-11-01</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>1586.198</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2006-12-01</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>1536.59</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2007-01-01</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>1556.011</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2007-02-01</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>1627.768</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2007-03-01</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>1746.754</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2007-04-01</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>1883.625</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2007-05-01</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>1966.094</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2007-06-01</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>2016.09</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2007-07-01</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>2094.66</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2007-08-01</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>2195.414</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2007-09-01</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>2191.938</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2007-10-01</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>2264.357</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2007-11-01</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>2235.081</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2007-12-01</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>2401.25</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2008-01-01</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>2306.953</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2008-02-01</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>2417.223</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2008-03-01</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>2454.756</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2008-04-01</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>2466.296</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2008-05-01</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>2516.226</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2008-06-01</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>2564.285</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2008-07-01</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>2595.183</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2008-08-01</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>2576.446</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2008-09-01</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>2522.346</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2008-10-01</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>2355.077</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2008-11-01</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>2239.114</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2008-12-01</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>2267.415</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2009-01-01</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>2199.368</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2009-02-01</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>2312.991</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2009-03-01</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>2350.936</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2009-04-01</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>2340.691</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2009-05-01</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>2403.511</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2009-06-01</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>2438.368</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2009-07-01</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>2509.089</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2009-08-01</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>2563.471</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2009-09-01</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>2652.385</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2009-10-01</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>2669.937</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2009-11-01</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>2714.14</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2009-12-01</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>2879.43</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>2870.393</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2010-02-01</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>2981.257</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2010-03-01</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>2973.912</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2010-04-01</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>3162.435</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2010-05-01</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>3251.587</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2010-06-01</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>3521.839</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2010-07-01</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>3540.947</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2010-08-01</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>3655.609</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2010-09-01</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>3850.189</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2010-10-01</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>3871.65</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2010-11-01</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>3938.209</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2010-12-01</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>4678.684</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2011-01-01</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>4804.182</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2011-02-01</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>4866.152</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2011-03-01</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>4953.94</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2011-04-01</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>5349.578</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2011-05-01</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>5428.282</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2011-06-01</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>5771.548</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2011-07-01</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>5919.386</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2011-08-01</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>5902.232</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2011-09-01</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>6049.324</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2011-10-01</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>6073.734</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2011-11-01</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>6112.144</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2011-12-01</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>6411.182</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2012-01-01</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>6146.034</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2012-02-01</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>6236.173</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2012-03-01</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>6102.589</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2012-04-01</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>6360.705</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2012-05-01</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>6727.36</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2012-06-01</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>7048.916</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2012-07-01</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>6951.219</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2012-08-01</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>6995.639</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2012-09-01</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>7110.345</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2012-10-01</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>7130.805</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2012-11-01</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>7031.391</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2012-12-01</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>7611.877</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2013-01-01</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>7338.853</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2013-02-01</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>7236.124</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2013-03-01</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>7298.742</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2013-04-01</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>7182.082</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2013-05-01</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>7906.683</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2013-06-01</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>8001.586</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2013-07-01</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>8086.234</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2013-08-01</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>8406.732</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2013-09-01</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>8476.620000000001</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2013-10-01</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>8712.044</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2013-11-01</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>9099.216</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2013-12-01</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>9452.552</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>10019.293</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2014-02-01</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>9845.624</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2014-03-01</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>9947.307000000001</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2014-04-01</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>10201.155</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2014-05-01</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>10238.368</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2014-06-01</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>10104.896</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2014-07-01</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>10076.029</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2014-08-01</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>10133.834</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2014-09-01</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>10072.141</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2014-10-01</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>9972.084999999999</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2014-11-01</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>9926.955</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2014-12-01</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>10634.331</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2015-01-01</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>10313.104</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2015-02-01</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>10228.989</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2015-03-01</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>9902.262000000001</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2015-04-01</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>9703.583000000001</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2015-05-01</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>9844.468999999999</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2015-06-01</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>10039.918</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2015-07-01</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>9860.65</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2015-08-01</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>9963.097</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2015-09-01</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>9933.224</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2015-10-01</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>9899.004000000001</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2015-11-01</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>9808.052</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2015-12-01</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>10048.996</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2016-01-01</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>9849.544</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2016-02-01</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>10011.025</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2016-03-01</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>10112.431</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2016-04-01</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>10517.392</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2016-05-01</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>10657.797</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2016-06-01</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>11186.374</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2016-07-01</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>11308.845</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2016-08-01</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>11379.761</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2016-09-01</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>11556.927</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2016-10-01</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>11612.008</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2016-11-01</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>11726.408</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2016-12-01</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>12158.53</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2017-01-01</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>11973.696</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2017-02-01</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>12324.741</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2017-03-01</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>12259.343</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2017-04-01</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>12467.829</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2017-05-01</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>12989.768</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2017-06-01</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>13483.236</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2017-07-01</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>13999.63</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2017-08-01</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>14526.296</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2017-09-01</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>14749.712</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2017-10-01</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>14520.672</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2017-11-01</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>14821.847</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2017-12-01</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>15861.199</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2018-01-01</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>15762.99</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2018-02-01</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>15913.169</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2018-03-01</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>16073.936</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2018-04-01</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>16240.148</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2018-05-01</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>17045.319</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2018-06-01</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>17342.874</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2018-07-01</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>17211.716</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2018-08-01</t>
+        </is>
+      </c>
+      <c r="B259" t="n">
+        <v>17440.406</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2018-09-01</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>17920.219</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2018-10-01</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>18332.538</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2018-11-01</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>18651.363</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2018-12-01</t>
+        </is>
+      </c>
+      <c r="B263" t="n">
+        <v>19474.698</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2019-01-01</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>19843.586</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2019-02-01</t>
+        </is>
+      </c>
+      <c r="B265" t="n">
+        <v>19796.175</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2019-03-01</t>
+        </is>
+      </c>
+      <c r="B266" t="n">
+        <v>19972.004</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2019-04-01</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>20146.632</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2019-05-01</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>20523.645</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2019-06-01</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>20441.392</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2019-07-01</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>20497.654</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2019-08-01</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>20685.415</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2019-09-01</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>20644.272</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2019-10-01</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>20682.23</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2019-11-01</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>20699.148</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2019-12-01</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>21063.592</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>20776.014</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2020-02-01</t>
+        </is>
+      </c>
+      <c r="B277" t="n">
+        <v>20839.406</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2020-03-01</t>
+        </is>
+      </c>
+      <c r="B278" t="n">
+        <v>20692.231</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2020-04-01</t>
+        </is>
+      </c>
+      <c r="B279" t="n">
+        <v>20476.376</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2020-05-01</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>20880.406</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>21592.062</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2020-07-01</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>21705.572</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2020-08-01</t>
+        </is>
+      </c>
+      <c r="B283" t="n">
+        <v>21747.046</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2020-09-01</t>
+        </is>
+      </c>
+      <c r="B284" t="n">
+        <v>22674.75</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2020-10-01</t>
+        </is>
+      </c>
+      <c r="B285" t="n">
+        <v>22785.286</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2020-11-01</t>
+        </is>
+      </c>
+      <c r="B286" t="n">
+        <v>23520.453</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2020-12-01</t>
+        </is>
+      </c>
+      <c r="B287" t="n">
+        <v>24480.748</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2021-01-01</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>24481.98</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2021-02-01</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>24914.844</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2021-03-01</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>25433.434</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2021-04-01</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>27045.373</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2021-05-01</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>27178.968</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2021-06-01</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>27974.093</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>27411.111</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2021-08-01</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>27411.347</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2021-09-01</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>27257.522</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2021-10-01</t>
+        </is>
+      </c>
+      <c r="B297" t="n">
+        <v>27071.448</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2021-11-01</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>27251.273</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2021-12-01</t>
+        </is>
+      </c>
+      <c r="B299" t="n">
+        <v>27863.477</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="B300" t="n">
+        <v>26807.327</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2022-02-01</t>
+        </is>
+      </c>
+      <c r="B301" t="n">
+        <v>26261.136</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2022-03-01</t>
+        </is>
+      </c>
+      <c r="B302" t="n">
+        <v>26483.149</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2022-04-01</t>
+        </is>
+      </c>
+      <c r="B303" t="n">
+        <v>27435.256</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2022-05-01</t>
+        </is>
+      </c>
+      <c r="B304" t="n">
+        <v>27502.19</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2022-06-01</t>
+        </is>
+      </c>
+      <c r="B305" t="n">
+        <v>27614.193</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="B306" t="n">
+        <v>27032.278</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2022-08-01</t>
+        </is>
+      </c>
+      <c r="B307" t="n">
+        <v>26944.134</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2022-09-01</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>27463.072</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2022-10-01</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>27282.945</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2022-11-01</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>27342.158</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2022-12-01</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
+        <v>29664.808</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="B312" t="n">
+        <v>29716.835</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2023-02-01</t>
+        </is>
+      </c>
+      <c r="B313" t="n">
+        <v>30242.669</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2023-03-01</t>
+        </is>
+      </c>
+      <c r="B314" t="n">
+        <v>30901.465</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2023-04-01</t>
+        </is>
+      </c>
+      <c r="B315" t="n">
+        <v>30165.252</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2023-05-01</t>
+        </is>
+      </c>
+      <c r="B316" t="n">
+        <v>30476.816</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2023-06-01</t>
+        </is>
+      </c>
+      <c r="B317" t="n">
+        <v>31392.6</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2023-07-01</t>
+        </is>
+      </c>
+      <c r="B318" t="n">
+        <v>31961.028</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2023-08-01</t>
+        </is>
+      </c>
+      <c r="B319" t="n">
+        <v>32531.817</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="B320" t="n">
+        <v>32856.354</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+      <c r="B321" t="n">
+        <v>33310.806</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2023-11-01</t>
+        </is>
+      </c>
+      <c r="B322" t="n">
+        <v>34910.196</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2023-12-01</t>
+        </is>
+      </c>
+      <c r="B323" t="n">
+        <v>36831.915</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
+        <v>36583.744</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2024-02-01</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>36746.3</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="B326" t="n">
+        <v>36590.413</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="B327" t="n">
+        <v>37084.4</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="B328" t="n">
+        <v>37975.371</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="B329" t="n">
+        <v>40515.291</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="B330" t="n">
+        <v>40753.955</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="B331" t="n">
+        <v>40649.418</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="B332" t="n">
+        <v>40890.271</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="B333" t="n">
+        <v>41120.05</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
+        </is>
+      </c>
+      <c r="B334" t="n">
+        <v>40498.782</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="B335" t="n">
+        <v>42551.313</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="B336" t="n">
+        <v>41051.244</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="B337" t="n">
+        <v>41087.804</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="B338" t="n">
+        <v>40745.178</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="B339" t="n">
+        <v>40706.403</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="B340" t="n">
+        <v>40772.661</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="B341" t="n">
+        <v>42229.631</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="B342" t="n">
+        <v>42424.486</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="B343" t="n">
+        <v>43618.017</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="B344" t="n">
+        <v>43434.414</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="B345" t="n">
+        <v>44359.869</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="B346" t="n">
+        <v>45161.918</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="B347" t="n">
+        <v>46776.739</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B348" t="n">
+        <v>46438.68</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B349" t="n">
+        <v>47666.139</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>48965.027</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>50384.647</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>51699.88</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>53145.303</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>53124.151</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data.mn/public/datasets/mongolbank-money-supply-m2.xlsx
+++ b/data.mn/public/datasets/mongolbank-money-supply-m2.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B354"/>
+  <dimension ref="A1:B356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3961,6 +3961,26 @@
       </c>
       <c r="B354" t="n">
         <v>53124.151</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>54400.98</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>56760.758</v>
       </c>
     </row>
   </sheetData>
@@ -3974,7 +3994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B354"/>
+  <dimension ref="A1:B356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7523,6 +7543,26 @@
         <v>53124.151</v>
       </c>
     </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>54400.98</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>56760.758</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
